--- a/ใบ177 Update.xlsx
+++ b/ใบ177 Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E57B859-4B50-437B-A81A-21D163ABA874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB55C218-07BE-4136-8C61-7C5EFB7BF9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>การรถไฟแห่งประเทศไทย</t>
   </si>
@@ -129,9 +129,6 @@
     <t>(นายทองปิ่น  จันทร์แปลง)</t>
   </si>
   <si>
-    <t>(นายปฐม  ชุมวงศ์)</t>
-  </si>
-  <si>
     <t>ผู้เบิก</t>
   </si>
   <si>
@@ -165,18 +162,9 @@
     <t>ประจำเดือน [13] พ.ศ. 2569</t>
   </si>
   <si>
-    <t xml:space="preserve">วันที่  [14]                                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">วันที่   [14]                                  </t>
-  </si>
-  <si>
     <t>[15] ([16])</t>
   </si>
   <si>
-    <t>ชื่อ  [NAME]      ตำแหน่ง  [1]      เลขประจำตัว  [2]      อัตราเงินเดือน  [3] บาท      ฝ่าย  ฝ่ายปฏิบัติการเดินรถ</t>
-  </si>
-  <si>
     <t>[SHIFT_1]</t>
   </si>
   <si>
@@ -186,14 +174,126 @@
     <t>([NAME])</t>
   </si>
   <si>
-    <t>รวม [17]</t>
+    <t>[1_2]</t>
+  </si>
+  <si>
+    <t>(นายปฐม  ชุมวงค์)</t>
+  </si>
+  <si>
+    <t>วันที่   [14]</t>
+  </si>
+  <si>
+    <t>วันที่  [14]</t>
+  </si>
+  <si>
+    <t>รวม [17] วัน</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ชื่อ  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="15"/>
+        <rFont val="TH SarabunPSK"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>[NAME]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <rFont val="TH SarabunPSK"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">   ตำแหน่ง  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="15"/>
+        <rFont val="TH SarabunPSK"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>[1]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <rFont val="TH SarabunPSK"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">  เลขประจำตัว  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="15"/>
+        <rFont val="TH SarabunPSK"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>[2]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <rFont val="TH SarabunPSK"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">   อัตราเงินเดือน  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="15"/>
+        <rFont val="TH SarabunPSK"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>[3]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <rFont val="TH SarabunPSK"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> บาท   ฝ่าย </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="15"/>
+        <rFont val="TH SarabunPSK"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ปฏิบัติการเดินรถ</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,6 +366,14 @@
       <name val="TH Sarabun New"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="15"/>
+      <name val="TH SarabunPSK"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -439,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -493,6 +601,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -518,10 +633,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -830,7 +944,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.44140625" customWidth="1"/>
@@ -843,132 +957,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
+      <c r="A3" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+    </row>
+    <row r="5" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21"/>
+      <c r="B5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-    </row>
-    <row r="5" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+    </row>
+    <row r="6" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D6" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="26" t="s">
+      <c r="E6" s="30"/>
+      <c r="F6" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="26" t="s">
+      <c r="G6" s="30"/>
+      <c r="H6" s="29" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="30"/>
-      <c r="B6" s="2" t="s">
+    <row r="7" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="33"/>
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="30"/>
-    </row>
-    <row r="7" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="5" t="s">
-        <v>13</v>
+      <c r="H8" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -977,12 +1089,12 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -991,12 +1103,12 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1005,12 +1117,12 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1019,12 +1131,12 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="5" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1033,12 +1145,12 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1047,12 +1159,12 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1061,12 +1173,12 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="5" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1074,13 +1186,13 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="6" t="s">
-        <v>39</v>
+      <c r="H16" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1089,12 +1201,12 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1102,13 +1214,13 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="5" t="s">
-        <v>18</v>
+      <c r="H18" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1117,12 +1229,12 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="5" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1131,12 +1243,12 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1144,13 +1256,13 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="7" t="s">
-        <v>7</v>
+      <c r="H21" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1158,11 +1270,13 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="5"/>
+      <c r="H22" s="7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1174,7 +1288,7 @@
     </row>
     <row r="24" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1186,7 +1300,7 @@
     </row>
     <row r="25" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1198,7 +1312,7 @@
     </row>
     <row r="26" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1210,7 +1324,7 @@
     </row>
     <row r="27" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1222,7 +1336,7 @@
     </row>
     <row r="28" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1234,7 +1348,7 @@
     </row>
     <row r="29" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1246,7 +1360,7 @@
     </row>
     <row r="30" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1258,7 +1372,7 @@
     </row>
     <row r="31" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1270,7 +1384,7 @@
     </row>
     <row r="32" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1278,13 +1392,11 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1293,12 +1405,12 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1307,12 +1419,12 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1321,12 +1433,12 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1335,105 +1447,109 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>30</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9">
+    <row r="38" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9">
         <v>31</v>
       </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="11" t="s">
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="34"/>
-      <c r="B38" s="10" t="s">
+    <row r="39" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="36"/>
+      <c r="B39" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="25">
-        <f>SUM(C7:C37)</f>
+      <c r="C39" s="28">
+        <f>SUM(C8:C38)</f>
         <v>0</v>
       </c>
-      <c r="D38" s="25">
-        <f>D37</f>
+      <c r="D39" s="28">
+        <f>D38</f>
         <v>0</v>
       </c>
-      <c r="E38" s="25">
-        <f>E37</f>
+      <c r="E39" s="28">
+        <f>E38</f>
         <v>0</v>
       </c>
-      <c r="F38" s="23">
-        <f>SUM(F7:F37)</f>
+      <c r="F39" s="26">
+        <f>SUM(F8:F38)</f>
         <v>0</v>
       </c>
-      <c r="G38" s="23">
-        <f>SUM(G7:G37)</f>
+      <c r="G39" s="26">
+        <f>SUM(G8:G38)</f>
         <v>0</v>
       </c>
-      <c r="H38" s="12" t="s">
+      <c r="H39" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="24"/>
-      <c r="B39" s="14" t="str">
-        <f>"(เงิน"&amp;BAHTTEXT(F38)&amp;")"</f>
+    <row r="40" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A40" s="27"/>
+      <c r="B40" s="14" t="str">
+        <f>"(เงิน"&amp;BAHTTEXT(F39)&amp;")"</f>
         <v>(เงินศูนย์บาทถ้วน)</v>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A40" s="19"/>
-      <c r="B40" s="17" t="s">
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A41" s="19"/>
+      <c r="B41" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C41" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="16" t="s">
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="16" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A41" s="18"/>
-      <c r="B41" s="16" t="s">
+    <row r="42" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A42" s="18"/>
+      <c r="B42" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C42" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -1446,72 +1562,82 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
-    <row r="44" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A44" s="15"/>
-      <c r="B44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="28" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A45" s="15"/>
+      <c r="B45" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B45" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
       <c r="H45" s="16" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B46" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
+        <v>32</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
       <c r="H46" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="16" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="F39:F40"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="C45:G45"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C42:G42"/>
     <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ใบ177 Update.xlsx
+++ b/ใบ177 Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB55C218-07BE-4136-8C61-7C5EFB7BF9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF0FAAC-B52B-486F-B071-677F74F0E21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -605,39 +605,39 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -957,59 +957,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
     </row>
     <row r="5" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21"/>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="36"/>
       <c r="D5" s="22"/>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
@@ -1029,17 +1029,17 @@
       <c r="D6" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="29" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
+      <c r="A7" s="30"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1058,7 +1058,7 @@
       <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="33"/>
+      <c r="H7" s="30"/>
     </row>
     <row r="8" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
@@ -1479,27 +1479,27 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="32">
         <f>SUM(C8:C38)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="28">
+      <c r="D39" s="32">
         <f>D38</f>
         <v>0</v>
       </c>
-      <c r="E39" s="28">
+      <c r="E39" s="32">
         <f>E38</f>
         <v>0</v>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="25">
         <f>SUM(F8:F38)</f>
         <v>0</v>
       </c>
-      <c r="G39" s="26">
+      <c r="G39" s="25">
         <f>SUM(G8:G38)</f>
         <v>0</v>
       </c>
@@ -1508,16 +1508,16 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="27"/>
+      <c r="A40" s="26"/>
       <c r="B40" s="14" t="str">
         <f>"(เงิน"&amp;BAHTTEXT(F39)&amp;")"</f>
         <v>(เงินศูนย์บาทถ้วน)</v>
       </c>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
       <c r="H40" s="13" t="s">
         <v>43</v>
       </c>
@@ -1527,13 +1527,13 @@
       <c r="B41" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="32" t="s">
+      <c r="C41" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
       <c r="H41" s="16" t="s">
         <v>28</v>
       </c>
@@ -1543,13 +1543,13 @@
       <c r="B42" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -1577,13 +1577,13 @@
       <c r="B45" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="31" t="s">
+      <c r="C45" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
       <c r="H45" s="16" t="s">
         <v>48</v>
       </c>
@@ -1592,13 +1592,13 @@
       <c r="B46" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="31" t="s">
+      <c r="C46" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
       <c r="H46" s="16" t="s">
         <v>34</v>
       </c>
@@ -1607,19 +1607,29 @@
       <c r="B47" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="31" t="s">
+      <c r="C47" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
       <c r="H47" s="16" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="C47:G47"/>
     <mergeCell ref="F39:F40"/>
     <mergeCell ref="A2:H2"/>
@@ -1630,15 +1640,6 @@
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="C46:G46"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/ใบ177 Update.xlsx
+++ b/ใบ177 Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF0FAAC-B52B-486F-B071-677F74F0E21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07ED2978-F43F-43A4-B20A-57055F1C3880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -293,7 +293,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,6 +374,13 @@
       <family val="2"/>
       <charset val="222"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="TH SarabunPSK"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -605,38 +612,38 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -957,7 +964,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="24"/>
@@ -969,7 +976,7 @@
       <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="24"/>
@@ -981,7 +988,7 @@
       <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="33" t="s">
         <v>42</v>
       </c>
       <c r="B3" s="24"/>
@@ -993,7 +1000,7 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="34" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="24"/>
@@ -1017,7 +1024,7 @@
       <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1026,20 +1033,20 @@
       <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="33"/>
-      <c r="F6" s="29" t="s">
+      <c r="E6" s="29"/>
+      <c r="F6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="29" t="s">
+      <c r="G6" s="29"/>
+      <c r="H6" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1058,7 +1065,7 @@
       <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="30"/>
+      <c r="H7" s="32"/>
     </row>
     <row r="8" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
@@ -1479,19 +1486,19 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="31"/>
+      <c r="A39" s="35"/>
       <c r="B39" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="27">
         <f>SUM(C8:C38)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="27">
         <f>D38</f>
         <v>0</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="27">
         <f>E38</f>
         <v>0</v>
       </c>
@@ -1527,7 +1534,7 @@
       <c r="B41" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="35" t="s">
+      <c r="C41" s="31" t="s">
         <v>27</v>
       </c>
       <c r="D41" s="24"/>
@@ -1543,7 +1550,7 @@
       <c r="B42" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="30" t="s">
         <v>30</v>
       </c>
       <c r="D42" s="24"/>
@@ -1577,7 +1584,7 @@
       <c r="B45" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="30" t="s">
         <v>31</v>
       </c>
       <c r="D45" s="24"/>
@@ -1592,7 +1599,7 @@
       <c r="B46" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="30" t="s">
         <v>33</v>
       </c>
       <c r="D46" s="24"/>
@@ -1607,7 +1614,7 @@
       <c r="B47" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="30" t="s">
         <v>49</v>
       </c>
       <c r="D47" s="24"/>
@@ -1620,6 +1627,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="C46:G46"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G39:G40"/>
     <mergeCell ref="E39:E40"/>
@@ -1630,16 +1647,6 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="C46:G46"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" fitToHeight="0" orientation="portrait" r:id="rId1"/>
